--- a/assets/docs/lop5/Am nhac - Lop 5.xlsx
+++ b/assets/docs/lop5/Am nhac - Lop 5.xlsx
@@ -660,7 +660,9 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
+          <t>Năng lực số Miền 3 (Cơ bản, bậc 2): Ở tiết nhạc cụ và Vận dụng – Sáng tạo tổng kết chủ đề “Khúc ca ngày mới”, HS luyện mẫu tiết tấu đệm cho bài Chim sơn ca
+Năng lực số Miền 2 (Cơ bản, bậc 2): Cả lớp nghe lại bản quay và nhận xét theo tiêu chí chiếu sẵn: gõ đúng mẫu tiết tấu, đều phách, hoà với giọng hát
+KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
         </is>
       </c>
     </row>
@@ -727,7 +729,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): HS nghe bản thu bài Lí đất giồng từ học liệu số, nhìn lời và mẫu gõ đệm trên màn hình để ôn đúng nhịp trước khi tập với nhạc cụ.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -793,7 +799,9 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở tiết tổng kết chủ đề “Giai điệu quê hương”, GV mở bản thu bài Lí đất giồng cùng một vài điệu lí khác của Nam Bộ; HS nghe
+Năng lực số Miền 3 (Cơ bản, bậc 2): Các nhóm dàn dựng tiết mục hát kết hợp gõ đệm và vận động; GV quay lại rồi chiếu chậm đoạn gõ đệm để mỗi nhóm nhìn thấy tay mình vào phách sớm hay…
+KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
         </is>
       </c>
     </row>
@@ -929,7 +937,9 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở tiết tổng kết chủ đề “Bay vào tương lai”, GV mở bản thu các bài đã học và chiếu mẫu tiết tấu nhịp hai bốn phóng to; HS nghe
+Năng lực số Miền 3 (Cơ bản, bậc 2): Các nhóm dàn dựng tiết mục hát kết hợp gõ đệm; GV quay lại rồi chiếu chậm đoạn gõ để mỗi nhóm nhìn thấy tay mình vào phách sớm hay muộn
+KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
         </is>
       </c>
     </row>
@@ -995,7 +1005,11 @@
           <t>14</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): HS xem video mẫu thể hiện tiết tấu và giai điệu bằng nhạc cụ trên màn hình, nhận ra chỗ mình gõ chưa đúng rồi tập lại theo mẫu.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1061,7 +1075,9 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần tổng kết chủ đề “Chào mùa xuân đến”, GV mở bản thu Xô-nát Ánh trăng từ học liệu số, chiếu kèm vài dòng giới thiệu về tác phẩm
+Năng lực số Miền 3 (Cơ bản, bậc 2): Ở phần Luyện tập, GV quay tiết mục tổng hợp hát – đệm nhạc cụ – vận động của từng nhóm rồi chiếu lên tivi
+KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
         </is>
       </c>
     </row>
@@ -1262,8 +1278,9 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>QPAN: Cho HS nghe/hát bài hát về biển, đảo quê hương; qua đó giới thiệu chủ quyền, quyền chủ quyền biển, đảo Việt Nam và gương dũng cảm cứu hộ, cứu nạn của cán bộ, chiến sĩ.
-KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Khám phá tổng kết chủ đề “Thiên nhiên tươi đẹp”, GV chiếu mẫu tiết tấu nhịp ba bốn lên màn hình và mở bản đệm mẫu cho bài Em đi giữa biển…
+Năng lực số Miền 3 (Cơ bản, bậc 2): Ở phần Vận dụng – Sáng tạo, GV ghi âm phần hoà tấu của từng nhóm rồi mở lại cho cả lớp nghe
+QPAN: Cho HS nghe/hát bài hát về biển, đảo quê hương; qua đó giới thiệu chủ quyền, quyền chủ quyền biển, đảo Việt Nam và gương dũng cảm cứu hộ, cứu nạn của cán bộ, chiến sĩ.</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1346,11 @@
           <t>24</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr"/>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 3 (Cơ bản, bậc 2): HS được GV ghi hình phần gõ đệm bài Tuổi hồng ơi của nhóm, xem lại trên tivi để chỉnh chỗ chưa khớp nhịp trước khi biểu diễn.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -1395,7 +1416,9 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Khởi động tổng kết chủ đề “Ước mơ tuổi thơ”, GV mở bản thu bài Tuổi hồng ơi từ học liệu số và chiếu lời lên màn hình
+Năng lực số Miền 3 (Cơ bản, bậc 2): Ở phần Vận dụng – Sáng tạo, GV quay tiết mục tổng hợp của từng nhóm rồi chiếu lên tivi; các nhóm tự xem lại để chỉnh chỗ vào nhạc chưa khớp
+KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1556,9 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Khởi động tổng kết chủ đề “Âm nhạc nước ngoài”, GV mở bản thu bài Đất nước tươi đẹp sao từ học liệu số và chiếu lời cùng tên nước lên màn…
+Năng lực số Miền 3 (Cơ bản, bậc 2): Ở phần Vận dụng – Sáng tạo, GV quay tiết mục của từng nhóm rồi chiếu lên tivi; các nhóm tự xem lại để chỉnh chỗ vào nhạc chưa khớp
+KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1660,9 @@
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Khởi động tổng kết chủ đề “Khúc ca hè về”, GV mở bản thu bài hát từ học liệu số và chiếu lời lên màn hình
+Năng lực số Miền 3 (Cơ bản, bậc 2): Ở phần Vận dụng – Sáng tạo, GV quay tiết mục của từng nhóm rồi chiếu lên tivi; các nhóm tự xem lại để chỉnh chỗ vào nhạc chưa khớp
+KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
         </is>
       </c>
     </row>

--- a/assets/docs/lop5/Am nhac - Lop 5.xlsx
+++ b/assets/docs/lop5/Am nhac - Lop 5.xlsx
@@ -535,7 +535,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: KHÚC CA NGÀY MỚI</t>
+          <t>Chủ đề 1: Khúc ca ngày mới</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr"/>
@@ -569,7 +569,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: KHÚC CA NGÀY MỚI</t>
+          <t>Chủ đề 1: Khúc ca ngày mới</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
@@ -603,7 +603,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: KHÚC CA NGÀY MỚI</t>
+          <t>Chủ đề 1: Khúc ca ngày mới</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr"/>
@@ -638,7 +638,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: KHÚC CA NGÀY MỚI</t>
+          <t>Chủ đề 1: Khúc ca ngày mới</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
@@ -674,7 +674,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: GIAI ĐIỆU QUÊ HƯƠNG</t>
+          <t>Chủ đề 2: Giai điệu quê hương</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: GIAI ĐIỆU QUÊ HƯƠNG</t>
+          <t>Chủ đề 2: Giai điệu quê hương</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
@@ -743,7 +743,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: GIAI ĐIỆU QUÊ HƯƠNG</t>
+          <t>Chủ đề 2: Giai điệu quê hương</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr"/>
@@ -777,7 +777,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: GIAI ĐIỆU QUÊ HƯƠNG</t>
+          <t>Chủ đề 2: Giai điệu quê hương</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
@@ -813,7 +813,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: BAY VÀO TƯƠNG LAI</t>
+          <t>Chủ đề 3: Bay vào tương lai</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: BAY VÀO TƯƠNG LAI</t>
+          <t>Chủ đề 3: Bay vào tương lai</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr"/>
@@ -881,7 +881,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: BAY VÀO TƯƠNG LAI</t>
+          <t>Chủ đề 3: Bay vào tương lai</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr"/>
@@ -915,7 +915,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: BAY VÀO TƯƠNG LAI</t>
+          <t>Chủ đề 3: Bay vào tương lai</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
@@ -951,7 +951,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: CHÀO MÙA XUÂN ĐẾN</t>
+          <t>Chủ đề 4: Chào mùa xuân đến</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: CHÀO MÙA XUÂN ĐẾN</t>
+          <t>Chủ đề 4: Chào mùa xuân đến</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: CHÀO MÙA XUÂN ĐẾN</t>
+          <t>Chủ đề 4: Chào mùa xuân đến</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr"/>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: CHÀO MÙA XUÂN ĐẾN</t>
+          <t>Chủ đề 4: Chào mùa xuân đến</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr"/>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: THIÊN NHIÊN TƯƠI ĐẸP</t>
+          <t>Chủ đề 5: Thiên nhiên tươi đẹp</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: THIÊN NHIÊN TƯƠI ĐẸP</t>
+          <t>Chủ đề 5: Thiên nhiên tươi đẹp</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr"/>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: THIÊN NHIÊN TƯƠI ĐẸP</t>
+          <t>Chủ đề 5: Thiên nhiên tươi đẹp</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr"/>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: THIÊN NHIÊN TƯƠI ĐẸP</t>
+          <t>Chủ đề 5: Thiên nhiên tươi đẹp</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr"/>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: ƯỚC MƠ TUỔI THƠ</t>
+          <t>Chủ đề 6: Ước mơ tuổi thơ</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr"/>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: ƯỚC MƠ TUỔI THƠ</t>
+          <t>Chủ đề 6: Ước mơ tuổi thơ</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr"/>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: ƯỚC MƠ TUỔI THƠ</t>
+          <t>Chủ đề 6: Ước mơ tuổi thơ</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr"/>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: ƯỚC MƠ TUỔI THƠ</t>
+          <t>Chủ đề 6: Ước mơ tuổi thơ</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr"/>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 7: ÂM NHẠC NƯỚC NGOÀI</t>
+          <t>Chủ đề 7: Âm nhạc nước ngoài</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr"/>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 7: ÂM NHẠC NƯỚC NGOÀI</t>
+          <t>Chủ đề 7: Âm nhạc nước ngoài</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr"/>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 7: ÂM NHẠC NƯỚC NGOÀI</t>
+          <t>Chủ đề 7: Âm nhạc nước ngoài</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr"/>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 7: ÂM NHẠC NƯỚC NGOÀI</t>
+          <t>Chủ đề 7: Âm nhạc nước ngoài</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr"/>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 8: KHÚC CA HÈ VỀ</t>
+          <t>Chủ đề 8: Khúc ca hè về</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr"/>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 8: KHÚC CA HÈ VỀ</t>
+          <t>Chủ đề 8: Khúc ca hè về</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr"/>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 8: KHÚC CA HÈ VỀ</t>
+          <t>Chủ đề 8: Khúc ca hè về</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr"/>
